--- a/outputs/out_dry.xlsx
+++ b/outputs/out_dry.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PerDisease" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PerReport" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ConfusionMatrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Predictions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,33 +414,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>disease</t>
+          <t>Disease</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>True Positive</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>False Negative</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>True Negative</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>False Positive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Positive Ground Truth</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Negative Ground Truth</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Ground Truth Check</t>
         </is>
       </c>
     </row>
@@ -454,13 +484,29 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -473,12 +519,28 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -500,6 +562,22 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,13 +589,29 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -538,6 +632,22 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,13 +659,29 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -576,6 +702,22 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -587,13 +729,29 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -606,12 +764,28 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -633,6 +807,22 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -652,6 +842,22 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -671,6 +877,22 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -690,6 +912,22 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -709,6 +947,22 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -728,6 +982,22 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -747,6 +1017,22 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -766,6 +1052,22 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -785,6 +1087,22 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -804,6 +1122,22 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,24 +1157,21 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vhs_v2</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,7 +1437,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1116,7 +1447,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,7 +1484,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1163,7 +1494,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1388,7 +1719,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1398,7 +1729,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1623,7 +1954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1633,7 +1964,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1844,53 +2175,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2771776</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>vhs_v2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Three orthogonal thoracic radiographs dated 29th September 2024 are available for review. There are no previous radiographs available for comparison. 
-Airway findings: A smoothly marginated soft tissue opacity is variably present overlying the dorsal aspect of the trachea at the thoracic inlet. This opacity reduces approximately 50% of the dorsoventral diameter of the trachea. The intrathoracic trachea is normal. Within the lung parenchyma there is a mixed bronchointerstitial opacification, predominantly caudal dorsally. The mainstem bronchi taper poorly. There is mild focal interstitial opacification in the left cranial lung lobe adjacent to the rib sections, however some obliquity is present. No associated osteolysis of the ribs is seen.
-Cardiovascular findings: The cardiac silhouette is normal in shape, size and margination. The cranial and caudal pulmonary vasculature is normal. The caudal vena cava is normal. The aorta and mainstem pulmonary artery have a normal outline in the vd/dv l image.
-Mediastinum and pleural space: There is some ventral pleural fat accumulation.
-Musculoskeletal findings: No significant abnormalities are detected.
-Included abdomen: No significant abnormalities are detected.</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>2770702</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1. The dorsal attenuation of the trachea is consistent with redundant trachealis membrane or overlying musculature. This may or may not be contributing towards the coughing.
-2. Diffuse moderate bronchointerstitial pattern: Some consideration should be given to normal ageing/fibrosis from previous disease. Allergic bronchitis, chronic bacterial /viral bronchitis +/- parasitic bronchitis should also be considered. Considering the mixed partial interstitial opacification, fungal disease needs to be excluded. Less likely are hyperardenocorticism, neoplasia (such a lymphoma) or idiopathic pulmonary fibrosis. The more localised left cranial interstitial opacification is most likely positional.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
